--- a/data/home-events.xlsx
+++ b/data/home-events.xlsx
@@ -445,7 +445,7 @@
         <v>previous</v>
       </c>
       <c r="B2" t="str">
-        <v xml:space="preserve">Ashadhi </v>
+        <v>Ashadhi Ekadashi</v>
       </c>
       <c r="C2" t="str">
         <v>July</v>
